--- a/output_excel/13786024.xlsx
+++ b/output_excel/13786024.xlsx
@@ -580,8 +580,16 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>ROD. GOV</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
@@ -632,7 +640,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>ROD. GOV</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
@@ -648,7 +660,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>C12X1000112,5KVAS45(1) | C12X1000112,5KVA2X[M1A]112,5KVAM3A112,5KVA2X[K52] | P31 P1-11 | 1AF(1) | (DCIM) | MT MT 3x185AX(5AZN) 3x185AX(5AZN) | B1F (DCIM) P4-30</t>
+          <t>C12X1000112,5KVAS45(1) | C12X1000112,5KVA2X[ M1A]112,5KVA2X[ M3A112,5KVA2X[K52] | P31 P1-11 | 1AF(1) | (DCIM) | MT MT 3x185AX(5AZN) 3x185AX(5AZN) | B1F (DCIM) P4-30</t>
         </is>
       </c>
       <c r="L3" s="3" t="n">
@@ -684,8 +696,16 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>ROD. GOV</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
@@ -737,7 +757,11 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
